--- a/artfynd/A 50389-2025 artfynd.xlsx
+++ b/artfynd/A 50389-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ3"/>
+  <dimension ref="A1:AZ18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,10 +680,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119283189</v>
+        <v>136531087</v>
       </c>
       <c r="B2" t="n">
-        <v>99038</v>
+        <v>99259</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,33 +691,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>223597</v>
+        <v>219790</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Jungfru marie nycklar</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. maculata</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr"/>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Sven-Jakobs, 400 m SV, Hjd</t>
+          <t>Z535 Åsarna, Hjd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>428769</v>
+        <v>428733</v>
       </c>
       <c r="R2" t="n">
-        <v>6965093</v>
+        <v>6965073</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -741,12 +745,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-07-01</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-07-01</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -757,160 +761,1746 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>Vägslänt</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Charlotte Wigermo</t>
+          <t>Väg och Miljö AB</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Charlotte Wigermo, Åke Svensson</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr"/>
+          <t>Väg och Miljö AB, Linn Andersson Linder</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119283189</t>
+          <t>https://artportalen.se/Sighting/136531087</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
+        <v>136533516</v>
+      </c>
+      <c r="B3" t="n">
+        <v>99259</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Z535 Åsarna, Hjd</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>428350</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6964787</v>
+      </c>
+      <c r="S3" t="n">
+        <v>3</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Åsarne</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB, Linn Andersson Linder</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136533516</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>136533705</v>
+      </c>
+      <c r="B4" t="n">
+        <v>99259</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Z535 Åsarna, Hjd</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>428589</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6964954</v>
+      </c>
+      <c r="S4" t="n">
+        <v>3</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Åsarne</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB, Linn Andersson Linder</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136533705</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>136536277</v>
+      </c>
+      <c r="B5" t="n">
+        <v>99259</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Z535 Åsarna, Hjd</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>428953</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6965262</v>
+      </c>
+      <c r="S5" t="n">
+        <v>4</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Åsarne</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB, Linn Andersson Linder</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136536277</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>136539184</v>
+      </c>
+      <c r="B6" t="n">
+        <v>99259</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Z535 Åsarna, Hjd</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>428560</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6964915</v>
+      </c>
+      <c r="S6" t="n">
+        <v>4</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Åsarne</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB, Linn Andersson Linder</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136539184</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>136548232</v>
+      </c>
+      <c r="B7" t="n">
+        <v>99259</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Z535 Åsarna, Hjd</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>428410</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6964817</v>
+      </c>
+      <c r="S7" t="n">
+        <v>5</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Åsarne</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB, Linn Andersson Linder</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136548232</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>136548347</v>
+      </c>
+      <c r="B8" t="n">
+        <v>99259</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Z535 Åsarna, Hjd</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>428754</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6965077</v>
+      </c>
+      <c r="S8" t="n">
+        <v>5</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Åsarne</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB, Linn Andersson Linder</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136548347</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>136530741</v>
+      </c>
+      <c r="B9" t="n">
+        <v>108105</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>219933</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Kattfot</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Antennaria dioica</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(L.) Gaertn.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Z535 Åsarna, Hjd</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>428765</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6965090</v>
+      </c>
+      <c r="S9" t="n">
+        <v>3</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Åsarne</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB, Linn Andersson Linder</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136530741</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>136531012</v>
+      </c>
+      <c r="B10" t="n">
+        <v>108105</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>219933</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Kattfot</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Antennaria dioica</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(L.) Gaertn.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Z535 Åsarna, Hjd</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>428697</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6965030</v>
+      </c>
+      <c r="S10" t="n">
+        <v>3</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Åsarne</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB, Linn Andersson Linder</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136531012</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>136533686</v>
+      </c>
+      <c r="B11" t="n">
+        <v>108105</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>219933</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Kattfot</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Antennaria dioica</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(L.) Gaertn.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Z535 Åsarna, Hjd</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>428831</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6965145</v>
+      </c>
+      <c r="S11" t="n">
+        <v>3</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Åsarne</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB, Linn Andersson Linder</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136533686</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>136534261</v>
+      </c>
+      <c r="B12" t="n">
+        <v>108105</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>219933</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Kattfot</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Antennaria dioica</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(L.) Gaertn.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Z535 Åsarna, Hjd</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>428658</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6965000</v>
+      </c>
+      <c r="S12" t="n">
+        <v>3</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Åsarne</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB, Linn Andersson Linder</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136534261</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>136534775</v>
+      </c>
+      <c r="B13" t="n">
+        <v>108105</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>219933</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Kattfot</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Antennaria dioica</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(L.) Gaertn.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Z535 Åsarna, Hjd</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>428556</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6964913</v>
+      </c>
+      <c r="S13" t="n">
+        <v>3</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Åsarne</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB, Linn Andersson Linder</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136534775</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>136538794</v>
+      </c>
+      <c r="B14" t="n">
+        <v>108105</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>219933</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Kattfot</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Antennaria dioica</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(L.) Gaertn.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Z535 Åsarna, Hjd</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>428388</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6964786</v>
+      </c>
+      <c r="S14" t="n">
+        <v>4</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Åsarne</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB, Linn Andersson Linder</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136538794</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>136551802</v>
+      </c>
+      <c r="B15" t="n">
+        <v>108105</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>219933</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Kattfot</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Antennaria dioica</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(L.) Gaertn.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Z535 Åsarna, Hjd</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>428929</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6965241</v>
+      </c>
+      <c r="S15" t="n">
+        <v>6</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Åsarne</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB, Linn Andersson Linder</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136551802</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>136552369</v>
+      </c>
+      <c r="B16" t="n">
+        <v>108105</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>219933</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Kattfot</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Antennaria dioica</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(L.) Gaertn.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Z535 Åsarna, Hjd</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>428881</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6965188</v>
+      </c>
+      <c r="S16" t="n">
+        <v>6</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Åsarne</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB, Linn Andersson Linder</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136552369</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>119283189</v>
+      </c>
+      <c r="B17" t="n">
+        <v>99038</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>223597</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Jungfru marie nycklar</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Sven-Jakobs, 400 m SV, Hjd</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>428769</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6965093</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Åsarne</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2024-07-01</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2024-07-01</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI17" t="inlineStr">
+        <is>
+          <t>Vägslänt</t>
+        </is>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Charlotte Wigermo</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Charlotte Wigermo, Åke Svensson</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119283189</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
         <v>113011959</v>
       </c>
-      <c r="B3" t="n">
+      <c r="B18" t="n">
         <v>108524</v>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="D18" t="inlineStr">
         <is>
           <t>DD</t>
         </is>
       </c>
-      <c r="E3" t="n">
+      <c r="E18" t="n">
         <v>231768</v>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="F18" t="inlineStr">
         <is>
           <t>Halsfibbla</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="G18" t="inlineStr">
         <is>
           <t>Hieracium longicollum</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="H18" t="inlineStr">
         <is>
           <t>(Dahlst. ex Zahn) Johanss. &amp; Sam.</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr">
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
         <is>
           <t>blomning</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
-      <c r="P3" t="inlineStr">
+      <c r="L18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
         <is>
           <t>Sven-Jakobs, 400 m SO om, Hjd</t>
         </is>
       </c>
-      <c r="Q3" t="n">
+      <c r="Q18" t="n">
         <v>428769</v>
       </c>
-      <c r="R3" t="n">
+      <c r="R18" t="n">
         <v>6965093</v>
       </c>
-      <c r="S3" t="n">
+      <c r="S18" t="n">
         <v>5</v>
       </c>
-      <c r="T3" t="inlineStr">
+      <c r="T18" t="inlineStr">
         <is>
           <t>Jämtland</t>
         </is>
       </c>
-      <c r="U3" t="inlineStr">
+      <c r="U18" t="inlineStr">
         <is>
           <t>Berg</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
+      <c r="V18" t="inlineStr">
         <is>
           <t>Härjedalen</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr">
+      <c r="W18" t="inlineStr">
         <is>
           <t>Åsarne</t>
         </is>
       </c>
-      <c r="Y3" t="inlineStr">
+      <c r="Y18" t="inlineStr">
         <is>
           <t>2023-07-10</t>
         </is>
       </c>
-      <c r="AA3" t="inlineStr">
+      <c r="AA18" t="inlineStr">
         <is>
           <t>2023-07-10</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
+      <c r="AC18" t="inlineStr">
         <is>
           <t>Belägg EJe-2023-086. Det. T. Tyler, LD, okt 2023. Endast ett tidigare fynd i Härjedalen, enligt Virtuella Herbariet; Hugo Dahlstedt 1905 i Storsjö.</t>
         </is>
       </c>
-      <c r="AD3" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE3" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF3" t="inlineStr"/>
-      <c r="AG3" t="b">
-        <v>0</v>
-      </c>
-      <c r="AI3" t="inlineStr">
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF18" t="inlineStr"/>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI18" t="inlineStr">
         <is>
           <t>Grusig vägren</t>
         </is>
       </c>
-      <c r="AP3" t="inlineStr">
+      <c r="AP18" t="inlineStr">
         <is>
           <t>Biologiska Museet, Lunds Universitet</t>
         </is>
       </c>
-      <c r="AS3" t="inlineStr">
+      <c r="AS18" t="inlineStr">
         <is>
           <t>Torbjörn Tyler</t>
         </is>
       </c>
-      <c r="AT3" t="inlineStr">
+      <c r="AT18" t="inlineStr">
         <is>
           <t>2023</t>
         </is>
       </c>
-      <c r="AW3" t="inlineStr">
+      <c r="AW18" t="inlineStr">
         <is>
           <t>Erling Jirle</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr">
+      <c r="AX18" t="inlineStr">
         <is>
           <t>Erling Jirle, Ola Elleström, Johan Lorentzon</t>
         </is>
       </c>
-      <c r="AY3" t="inlineStr"/>
-      <c r="AZ3" t="inlineStr">
+      <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/113011959</t>
         </is>
@@ -920,6 +2510,21 @@
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 50389-2025 artfynd.xlsx
+++ b/artfynd/A 50389-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136531087</v>
       </c>
       <c r="B2" t="n">
-        <v>99259</v>
+        <v>99262</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136533516</v>
       </c>
       <c r="B3" t="n">
-        <v>99259</v>
+        <v>99262</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>136533705</v>
       </c>
       <c r="B4" t="n">
-        <v>99259</v>
+        <v>99262</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>136536277</v>
       </c>
       <c r="B5" t="n">
-        <v>99259</v>
+        <v>99262</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1107,7 +1107,7 @@
         <v>136539184</v>
       </c>
       <c r="B6" t="n">
-        <v>99259</v>
+        <v>99262</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>136548232</v>
       </c>
       <c r="B7" t="n">
-        <v>99259</v>
+        <v>99262</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1319,7 +1319,7 @@
         <v>136548347</v>
       </c>
       <c r="B8" t="n">
-        <v>99259</v>
+        <v>99262</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1425,7 +1425,7 @@
         <v>136530741</v>
       </c>
       <c r="B9" t="n">
-        <v>108105</v>
+        <v>108108</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1531,7 +1531,7 @@
         <v>136531012</v>
       </c>
       <c r="B10" t="n">
-        <v>108105</v>
+        <v>108108</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1637,7 +1637,7 @@
         <v>136533686</v>
       </c>
       <c r="B11" t="n">
-        <v>108105</v>
+        <v>108108</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1743,7 +1743,7 @@
         <v>136534261</v>
       </c>
       <c r="B12" t="n">
-        <v>108105</v>
+        <v>108108</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1849,7 +1849,7 @@
         <v>136534775</v>
       </c>
       <c r="B13" t="n">
-        <v>108105</v>
+        <v>108108</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1955,7 +1955,7 @@
         <v>136538794</v>
       </c>
       <c r="B14" t="n">
-        <v>108105</v>
+        <v>108108</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2061,7 +2061,7 @@
         <v>136551802</v>
       </c>
       <c r="B15" t="n">
-        <v>108105</v>
+        <v>108108</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2167,7 +2167,7 @@
         <v>136552369</v>
       </c>
       <c r="B16" t="n">
-        <v>108105</v>
+        <v>108108</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 50389-2025 artfynd.xlsx
+++ b/artfynd/A 50389-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136531087</v>
       </c>
       <c r="B2" t="n">
-        <v>99262</v>
+        <v>99263</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136533516</v>
       </c>
       <c r="B3" t="n">
-        <v>99262</v>
+        <v>99263</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>136533705</v>
       </c>
       <c r="B4" t="n">
-        <v>99262</v>
+        <v>99263</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>136536277</v>
       </c>
       <c r="B5" t="n">
-        <v>99262</v>
+        <v>99263</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1107,7 +1107,7 @@
         <v>136539184</v>
       </c>
       <c r="B6" t="n">
-        <v>99262</v>
+        <v>99263</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>136548232</v>
       </c>
       <c r="B7" t="n">
-        <v>99262</v>
+        <v>99263</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1319,7 +1319,7 @@
         <v>136548347</v>
       </c>
       <c r="B8" t="n">
-        <v>99262</v>
+        <v>99263</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1425,7 +1425,7 @@
         <v>136530741</v>
       </c>
       <c r="B9" t="n">
-        <v>108108</v>
+        <v>108109</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1531,7 +1531,7 @@
         <v>136531012</v>
       </c>
       <c r="B10" t="n">
-        <v>108108</v>
+        <v>108109</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1637,7 +1637,7 @@
         <v>136533686</v>
       </c>
       <c r="B11" t="n">
-        <v>108108</v>
+        <v>108109</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1743,7 +1743,7 @@
         <v>136534261</v>
       </c>
       <c r="B12" t="n">
-        <v>108108</v>
+        <v>108109</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1849,7 +1849,7 @@
         <v>136534775</v>
       </c>
       <c r="B13" t="n">
-        <v>108108</v>
+        <v>108109</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1955,7 +1955,7 @@
         <v>136538794</v>
       </c>
       <c r="B14" t="n">
-        <v>108108</v>
+        <v>108109</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2061,7 +2061,7 @@
         <v>136551802</v>
       </c>
       <c r="B15" t="n">
-        <v>108108</v>
+        <v>108109</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2167,7 +2167,7 @@
         <v>136552369</v>
       </c>
       <c r="B16" t="n">
-        <v>108108</v>
+        <v>108109</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 50389-2025 artfynd.xlsx
+++ b/artfynd/A 50389-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136531087</v>
       </c>
       <c r="B2" t="n">
-        <v>99263</v>
+        <v>99268</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136533516</v>
       </c>
       <c r="B3" t="n">
-        <v>99263</v>
+        <v>99268</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>136533705</v>
       </c>
       <c r="B4" t="n">
-        <v>99263</v>
+        <v>99268</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>136536277</v>
       </c>
       <c r="B5" t="n">
-        <v>99263</v>
+        <v>99268</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1107,7 +1107,7 @@
         <v>136539184</v>
       </c>
       <c r="B6" t="n">
-        <v>99263</v>
+        <v>99268</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>136548232</v>
       </c>
       <c r="B7" t="n">
-        <v>99263</v>
+        <v>99268</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1319,7 +1319,7 @@
         <v>136548347</v>
       </c>
       <c r="B8" t="n">
-        <v>99263</v>
+        <v>99268</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1425,7 +1425,7 @@
         <v>136530741</v>
       </c>
       <c r="B9" t="n">
-        <v>108109</v>
+        <v>108114</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1531,7 +1531,7 @@
         <v>136531012</v>
       </c>
       <c r="B10" t="n">
-        <v>108109</v>
+        <v>108114</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1637,7 +1637,7 @@
         <v>136533686</v>
       </c>
       <c r="B11" t="n">
-        <v>108109</v>
+        <v>108114</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1743,7 +1743,7 @@
         <v>136534261</v>
       </c>
       <c r="B12" t="n">
-        <v>108109</v>
+        <v>108114</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1849,7 +1849,7 @@
         <v>136534775</v>
       </c>
       <c r="B13" t="n">
-        <v>108109</v>
+        <v>108114</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1955,7 +1955,7 @@
         <v>136538794</v>
       </c>
       <c r="B14" t="n">
-        <v>108109</v>
+        <v>108114</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2061,7 +2061,7 @@
         <v>136551802</v>
       </c>
       <c r="B15" t="n">
-        <v>108109</v>
+        <v>108114</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2167,7 +2167,7 @@
         <v>136552369</v>
       </c>
       <c r="B16" t="n">
-        <v>108109</v>
+        <v>108114</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 50389-2025 artfynd.xlsx
+++ b/artfynd/A 50389-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136531087</v>
       </c>
       <c r="B2" t="n">
-        <v>99268</v>
+        <v>99270</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136533516</v>
       </c>
       <c r="B3" t="n">
-        <v>99268</v>
+        <v>99270</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>136533705</v>
       </c>
       <c r="B4" t="n">
-        <v>99268</v>
+        <v>99270</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>136536277</v>
       </c>
       <c r="B5" t="n">
-        <v>99268</v>
+        <v>99270</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1107,7 +1107,7 @@
         <v>136539184</v>
       </c>
       <c r="B6" t="n">
-        <v>99268</v>
+        <v>99270</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>136548232</v>
       </c>
       <c r="B7" t="n">
-        <v>99268</v>
+        <v>99270</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1319,7 +1319,7 @@
         <v>136548347</v>
       </c>
       <c r="B8" t="n">
-        <v>99268</v>
+        <v>99270</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1425,7 +1425,7 @@
         <v>136530741</v>
       </c>
       <c r="B9" t="n">
-        <v>108114</v>
+        <v>108116</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1531,7 +1531,7 @@
         <v>136531012</v>
       </c>
       <c r="B10" t="n">
-        <v>108114</v>
+        <v>108116</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1637,7 +1637,7 @@
         <v>136533686</v>
       </c>
       <c r="B11" t="n">
-        <v>108114</v>
+        <v>108116</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1743,7 +1743,7 @@
         <v>136534261</v>
       </c>
       <c r="B12" t="n">
-        <v>108114</v>
+        <v>108116</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1849,7 +1849,7 @@
         <v>136534775</v>
       </c>
       <c r="B13" t="n">
-        <v>108114</v>
+        <v>108116</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1955,7 +1955,7 @@
         <v>136538794</v>
       </c>
       <c r="B14" t="n">
-        <v>108114</v>
+        <v>108116</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2061,7 +2061,7 @@
         <v>136551802</v>
       </c>
       <c r="B15" t="n">
-        <v>108114</v>
+        <v>108116</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2167,7 +2167,7 @@
         <v>136552369</v>
       </c>
       <c r="B16" t="n">
-        <v>108114</v>
+        <v>108116</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 50389-2025 artfynd.xlsx
+++ b/artfynd/A 50389-2025 artfynd.xlsx
@@ -1300,7 +1300,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Väg och Miljö AB, Linn Andersson Linder</t>
+          <t>Linn Andersson Linder, Väg och Miljö AB</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">

--- a/artfynd/A 50389-2025 artfynd.xlsx
+++ b/artfynd/A 50389-2025 artfynd.xlsx
@@ -1300,7 +1300,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Linn Andersson Linder, Väg och Miljö AB</t>
+          <t>Väg och Miljö AB, Linn Andersson Linder</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
@@ -2254,7 +2254,7 @@
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Väg och Miljö AB, Linn Andersson Linder</t>
+          <t>Linn Andersson Linder, Väg och Miljö AB</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">

--- a/artfynd/A 50389-2025 artfynd.xlsx
+++ b/artfynd/A 50389-2025 artfynd.xlsx
@@ -2254,7 +2254,7 @@
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Linn Andersson Linder, Väg och Miljö AB</t>
+          <t>Väg och Miljö AB, Linn Andersson Linder</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">

--- a/artfynd/A 50389-2025 artfynd.xlsx
+++ b/artfynd/A 50389-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136531087</v>
       </c>
       <c r="B2" t="n">
-        <v>99270</v>
+        <v>99276</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136533516</v>
       </c>
       <c r="B3" t="n">
-        <v>99270</v>
+        <v>99276</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>136533705</v>
       </c>
       <c r="B4" t="n">
-        <v>99270</v>
+        <v>99276</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>136536277</v>
       </c>
       <c r="B5" t="n">
-        <v>99270</v>
+        <v>99276</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1107,7 +1107,7 @@
         <v>136539184</v>
       </c>
       <c r="B6" t="n">
-        <v>99270</v>
+        <v>99276</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>136548232</v>
       </c>
       <c r="B7" t="n">
-        <v>99270</v>
+        <v>99276</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1319,7 +1319,7 @@
         <v>136548347</v>
       </c>
       <c r="B8" t="n">
-        <v>99270</v>
+        <v>99276</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1425,7 +1425,7 @@
         <v>136530741</v>
       </c>
       <c r="B9" t="n">
-        <v>108116</v>
+        <v>108122</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1531,7 +1531,7 @@
         <v>136531012</v>
       </c>
       <c r="B10" t="n">
-        <v>108116</v>
+        <v>108122</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1637,7 +1637,7 @@
         <v>136533686</v>
       </c>
       <c r="B11" t="n">
-        <v>108116</v>
+        <v>108122</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1743,7 +1743,7 @@
         <v>136534261</v>
       </c>
       <c r="B12" t="n">
-        <v>108116</v>
+        <v>108122</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1849,7 +1849,7 @@
         <v>136534775</v>
       </c>
       <c r="B13" t="n">
-        <v>108116</v>
+        <v>108122</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1955,7 +1955,7 @@
         <v>136538794</v>
       </c>
       <c r="B14" t="n">
-        <v>108116</v>
+        <v>108122</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2061,7 +2061,7 @@
         <v>136551802</v>
       </c>
       <c r="B15" t="n">
-        <v>108116</v>
+        <v>108122</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2167,7 +2167,7 @@
         <v>136552369</v>
       </c>
       <c r="B16" t="n">
-        <v>108116</v>
+        <v>108122</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 50389-2025 artfynd.xlsx
+++ b/artfynd/A 50389-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136531087</v>
       </c>
       <c r="B2" t="n">
-        <v>99276</v>
+        <v>99278</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136533516</v>
       </c>
       <c r="B3" t="n">
-        <v>99276</v>
+        <v>99278</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>136533705</v>
       </c>
       <c r="B4" t="n">
-        <v>99276</v>
+        <v>99278</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>136536277</v>
       </c>
       <c r="B5" t="n">
-        <v>99276</v>
+        <v>99278</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1107,7 +1107,7 @@
         <v>136539184</v>
       </c>
       <c r="B6" t="n">
-        <v>99276</v>
+        <v>99278</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>136548232</v>
       </c>
       <c r="B7" t="n">
-        <v>99276</v>
+        <v>99278</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1319,7 +1319,7 @@
         <v>136548347</v>
       </c>
       <c r="B8" t="n">
-        <v>99276</v>
+        <v>99278</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1425,7 +1425,7 @@
         <v>136530741</v>
       </c>
       <c r="B9" t="n">
-        <v>108122</v>
+        <v>108124</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1531,7 +1531,7 @@
         <v>136531012</v>
       </c>
       <c r="B10" t="n">
-        <v>108122</v>
+        <v>108124</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1637,7 +1637,7 @@
         <v>136533686</v>
       </c>
       <c r="B11" t="n">
-        <v>108122</v>
+        <v>108124</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1743,7 +1743,7 @@
         <v>136534261</v>
       </c>
       <c r="B12" t="n">
-        <v>108122</v>
+        <v>108124</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1849,7 +1849,7 @@
         <v>136534775</v>
       </c>
       <c r="B13" t="n">
-        <v>108122</v>
+        <v>108124</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1955,7 +1955,7 @@
         <v>136538794</v>
       </c>
       <c r="B14" t="n">
-        <v>108122</v>
+        <v>108124</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2061,7 +2061,7 @@
         <v>136551802</v>
       </c>
       <c r="B15" t="n">
-        <v>108122</v>
+        <v>108124</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2167,7 +2167,7 @@
         <v>136552369</v>
       </c>
       <c r="B16" t="n">
-        <v>108122</v>
+        <v>108124</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 50389-2025 artfynd.xlsx
+++ b/artfynd/A 50389-2025 artfynd.xlsx
@@ -1194,7 +1194,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Väg och Miljö AB, Linn Andersson Linder</t>
+          <t>Linn Andersson Linder, Väg och Miljö AB</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">

--- a/artfynd/A 50389-2025 artfynd.xlsx
+++ b/artfynd/A 50389-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136531087</v>
       </c>
       <c r="B2" t="n">
-        <v>99278</v>
+        <v>99279</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136533516</v>
       </c>
       <c r="B3" t="n">
-        <v>99278</v>
+        <v>99279</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>136533705</v>
       </c>
       <c r="B4" t="n">
-        <v>99278</v>
+        <v>99279</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>136536277</v>
       </c>
       <c r="B5" t="n">
-        <v>99278</v>
+        <v>99279</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1107,7 +1107,7 @@
         <v>136539184</v>
       </c>
       <c r="B6" t="n">
-        <v>99278</v>
+        <v>99279</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1194,7 +1194,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Linn Andersson Linder, Väg och Miljö AB</t>
+          <t>Väg och Miljö AB, Linn Andersson Linder</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
@@ -1213,7 +1213,7 @@
         <v>136548232</v>
       </c>
       <c r="B7" t="n">
-        <v>99278</v>
+        <v>99279</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1319,7 +1319,7 @@
         <v>136548347</v>
       </c>
       <c r="B8" t="n">
-        <v>99278</v>
+        <v>99279</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1425,7 +1425,7 @@
         <v>136530741</v>
       </c>
       <c r="B9" t="n">
-        <v>108124</v>
+        <v>108125</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1531,7 +1531,7 @@
         <v>136531012</v>
       </c>
       <c r="B10" t="n">
-        <v>108124</v>
+        <v>108125</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1637,7 +1637,7 @@
         <v>136533686</v>
       </c>
       <c r="B11" t="n">
-        <v>108124</v>
+        <v>108125</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1743,7 +1743,7 @@
         <v>136534261</v>
       </c>
       <c r="B12" t="n">
-        <v>108124</v>
+        <v>108125</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1849,7 +1849,7 @@
         <v>136534775</v>
       </c>
       <c r="B13" t="n">
-        <v>108124</v>
+        <v>108125</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1955,7 +1955,7 @@
         <v>136538794</v>
       </c>
       <c r="B14" t="n">
-        <v>108124</v>
+        <v>108125</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2061,7 +2061,7 @@
         <v>136551802</v>
       </c>
       <c r="B15" t="n">
-        <v>108124</v>
+        <v>108125</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2167,7 +2167,7 @@
         <v>136552369</v>
       </c>
       <c r="B16" t="n">
-        <v>108124</v>
+        <v>108125</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 50389-2025 artfynd.xlsx
+++ b/artfynd/A 50389-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136531087</v>
       </c>
       <c r="B2" t="n">
-        <v>99279</v>
+        <v>99285</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136533516</v>
       </c>
       <c r="B3" t="n">
-        <v>99279</v>
+        <v>99285</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>136533705</v>
       </c>
       <c r="B4" t="n">
-        <v>99279</v>
+        <v>99285</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>136536277</v>
       </c>
       <c r="B5" t="n">
-        <v>99279</v>
+        <v>99285</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1107,7 +1107,7 @@
         <v>136539184</v>
       </c>
       <c r="B6" t="n">
-        <v>99279</v>
+        <v>99285</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>136548232</v>
       </c>
       <c r="B7" t="n">
-        <v>99279</v>
+        <v>99285</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1319,7 +1319,7 @@
         <v>136548347</v>
       </c>
       <c r="B8" t="n">
-        <v>99279</v>
+        <v>99285</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1425,7 +1425,7 @@
         <v>136530741</v>
       </c>
       <c r="B9" t="n">
-        <v>108125</v>
+        <v>108131</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1531,7 +1531,7 @@
         <v>136531012</v>
       </c>
       <c r="B10" t="n">
-        <v>108125</v>
+        <v>108131</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1637,7 +1637,7 @@
         <v>136533686</v>
       </c>
       <c r="B11" t="n">
-        <v>108125</v>
+        <v>108131</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1743,7 +1743,7 @@
         <v>136534261</v>
       </c>
       <c r="B12" t="n">
-        <v>108125</v>
+        <v>108131</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1849,7 +1849,7 @@
         <v>136534775</v>
       </c>
       <c r="B13" t="n">
-        <v>108125</v>
+        <v>108131</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1955,7 +1955,7 @@
         <v>136538794</v>
       </c>
       <c r="B14" t="n">
-        <v>108125</v>
+        <v>108131</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2061,7 +2061,7 @@
         <v>136551802</v>
       </c>
       <c r="B15" t="n">
-        <v>108125</v>
+        <v>108131</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2167,7 +2167,7 @@
         <v>136552369</v>
       </c>
       <c r="B16" t="n">
-        <v>108125</v>
+        <v>108131</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 50389-2025 artfynd.xlsx
+++ b/artfynd/A 50389-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136531087</v>
       </c>
       <c r="B2" t="n">
-        <v>99285</v>
+        <v>99289</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136533516</v>
       </c>
       <c r="B3" t="n">
-        <v>99285</v>
+        <v>99289</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>136533705</v>
       </c>
       <c r="B4" t="n">
-        <v>99285</v>
+        <v>99289</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>136536277</v>
       </c>
       <c r="B5" t="n">
-        <v>99285</v>
+        <v>99289</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1107,7 +1107,7 @@
         <v>136539184</v>
       </c>
       <c r="B6" t="n">
-        <v>99285</v>
+        <v>99289</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>136548232</v>
       </c>
       <c r="B7" t="n">
-        <v>99285</v>
+        <v>99289</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1319,7 +1319,7 @@
         <v>136548347</v>
       </c>
       <c r="B8" t="n">
-        <v>99285</v>
+        <v>99289</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1425,7 +1425,7 @@
         <v>136530741</v>
       </c>
       <c r="B9" t="n">
-        <v>108131</v>
+        <v>108135</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1531,7 +1531,7 @@
         <v>136531012</v>
       </c>
       <c r="B10" t="n">
-        <v>108131</v>
+        <v>108135</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1637,7 +1637,7 @@
         <v>136533686</v>
       </c>
       <c r="B11" t="n">
-        <v>108131</v>
+        <v>108135</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1743,7 +1743,7 @@
         <v>136534261</v>
       </c>
       <c r="B12" t="n">
-        <v>108131</v>
+        <v>108135</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1849,7 +1849,7 @@
         <v>136534775</v>
       </c>
       <c r="B13" t="n">
-        <v>108131</v>
+        <v>108135</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1955,7 +1955,7 @@
         <v>136538794</v>
       </c>
       <c r="B14" t="n">
-        <v>108131</v>
+        <v>108135</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2061,7 +2061,7 @@
         <v>136551802</v>
       </c>
       <c r="B15" t="n">
-        <v>108131</v>
+        <v>108135</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2167,7 +2167,7 @@
         <v>136552369</v>
       </c>
       <c r="B16" t="n">
-        <v>108131</v>
+        <v>108135</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 50389-2025 artfynd.xlsx
+++ b/artfynd/A 50389-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136531087</v>
       </c>
       <c r="B2" t="n">
-        <v>99289</v>
+        <v>99291</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136533516</v>
       </c>
       <c r="B3" t="n">
-        <v>99289</v>
+        <v>99291</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>136533705</v>
       </c>
       <c r="B4" t="n">
-        <v>99289</v>
+        <v>99291</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>136536277</v>
       </c>
       <c r="B5" t="n">
-        <v>99289</v>
+        <v>99291</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1107,7 +1107,7 @@
         <v>136539184</v>
       </c>
       <c r="B6" t="n">
-        <v>99289</v>
+        <v>99291</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>136548232</v>
       </c>
       <c r="B7" t="n">
-        <v>99289</v>
+        <v>99291</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1319,7 +1319,7 @@
         <v>136548347</v>
       </c>
       <c r="B8" t="n">
-        <v>99289</v>
+        <v>99291</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1425,7 +1425,7 @@
         <v>136530741</v>
       </c>
       <c r="B9" t="n">
-        <v>108135</v>
+        <v>108137</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1531,7 +1531,7 @@
         <v>136531012</v>
       </c>
       <c r="B10" t="n">
-        <v>108135</v>
+        <v>108137</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1637,7 +1637,7 @@
         <v>136533686</v>
       </c>
       <c r="B11" t="n">
-        <v>108135</v>
+        <v>108137</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1743,7 +1743,7 @@
         <v>136534261</v>
       </c>
       <c r="B12" t="n">
-        <v>108135</v>
+        <v>108137</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1849,7 +1849,7 @@
         <v>136534775</v>
       </c>
       <c r="B13" t="n">
-        <v>108135</v>
+        <v>108137</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1955,7 +1955,7 @@
         <v>136538794</v>
       </c>
       <c r="B14" t="n">
-        <v>108135</v>
+        <v>108137</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2061,7 +2061,7 @@
         <v>136551802</v>
       </c>
       <c r="B15" t="n">
-        <v>108135</v>
+        <v>108137</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2167,7 +2167,7 @@
         <v>136552369</v>
       </c>
       <c r="B16" t="n">
-        <v>108135</v>
+        <v>108137</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 50389-2025 artfynd.xlsx
+++ b/artfynd/A 50389-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136531087</v>
       </c>
       <c r="B2" t="n">
-        <v>99291</v>
+        <v>99293</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136533516</v>
       </c>
       <c r="B3" t="n">
-        <v>99291</v>
+        <v>99293</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>136533705</v>
       </c>
       <c r="B4" t="n">
-        <v>99291</v>
+        <v>99293</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>136536277</v>
       </c>
       <c r="B5" t="n">
-        <v>99291</v>
+        <v>99293</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1107,7 +1107,7 @@
         <v>136539184</v>
       </c>
       <c r="B6" t="n">
-        <v>99291</v>
+        <v>99293</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>136548232</v>
       </c>
       <c r="B7" t="n">
-        <v>99291</v>
+        <v>99293</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1300,7 +1300,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Väg och Miljö AB, Linn Andersson Linder</t>
+          <t>Linn Andersson Linder, Väg och Miljö AB</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
@@ -1319,7 +1319,7 @@
         <v>136548347</v>
       </c>
       <c r="B8" t="n">
-        <v>99291</v>
+        <v>99293</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1425,7 +1425,7 @@
         <v>136530741</v>
       </c>
       <c r="B9" t="n">
-        <v>108137</v>
+        <v>108139</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1531,7 +1531,7 @@
         <v>136531012</v>
       </c>
       <c r="B10" t="n">
-        <v>108137</v>
+        <v>108139</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1637,7 +1637,7 @@
         <v>136533686</v>
       </c>
       <c r="B11" t="n">
-        <v>108137</v>
+        <v>108139</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1743,7 +1743,7 @@
         <v>136534261</v>
       </c>
       <c r="B12" t="n">
-        <v>108137</v>
+        <v>108139</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1849,7 +1849,7 @@
         <v>136534775</v>
       </c>
       <c r="B13" t="n">
-        <v>108137</v>
+        <v>108139</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1955,7 +1955,7 @@
         <v>136538794</v>
       </c>
       <c r="B14" t="n">
-        <v>108137</v>
+        <v>108139</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2061,7 +2061,7 @@
         <v>136551802</v>
       </c>
       <c r="B15" t="n">
-        <v>108137</v>
+        <v>108139</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2167,7 +2167,7 @@
         <v>136552369</v>
       </c>
       <c r="B16" t="n">
-        <v>108137</v>
+        <v>108139</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 50389-2025 artfynd.xlsx
+++ b/artfynd/A 50389-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136531087</v>
       </c>
       <c r="B2" t="n">
-        <v>99293</v>
+        <v>99306</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136533516</v>
       </c>
       <c r="B3" t="n">
-        <v>99293</v>
+        <v>99306</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>136533705</v>
       </c>
       <c r="B4" t="n">
-        <v>99293</v>
+        <v>99306</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>136536277</v>
       </c>
       <c r="B5" t="n">
-        <v>99293</v>
+        <v>99306</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1107,7 +1107,7 @@
         <v>136539184</v>
       </c>
       <c r="B6" t="n">
-        <v>99293</v>
+        <v>99306</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>136548232</v>
       </c>
       <c r="B7" t="n">
-        <v>99293</v>
+        <v>99306</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1300,7 +1300,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Linn Andersson Linder, Väg och Miljö AB</t>
+          <t>Väg och Miljö AB, Linn Andersson Linder</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
@@ -1319,7 +1319,7 @@
         <v>136548347</v>
       </c>
       <c r="B8" t="n">
-        <v>99293</v>
+        <v>99306</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1425,7 +1425,7 @@
         <v>136530741</v>
       </c>
       <c r="B9" t="n">
-        <v>108139</v>
+        <v>108152</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1531,7 +1531,7 @@
         <v>136531012</v>
       </c>
       <c r="B10" t="n">
-        <v>108139</v>
+        <v>108152</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1637,7 +1637,7 @@
         <v>136533686</v>
       </c>
       <c r="B11" t="n">
-        <v>108139</v>
+        <v>108152</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1743,7 +1743,7 @@
         <v>136534261</v>
       </c>
       <c r="B12" t="n">
-        <v>108139</v>
+        <v>108152</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1849,7 +1849,7 @@
         <v>136534775</v>
       </c>
       <c r="B13" t="n">
-        <v>108139</v>
+        <v>108152</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1955,7 +1955,7 @@
         <v>136538794</v>
       </c>
       <c r="B14" t="n">
-        <v>108139</v>
+        <v>108152</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2061,7 +2061,7 @@
         <v>136551802</v>
       </c>
       <c r="B15" t="n">
-        <v>108139</v>
+        <v>108152</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2167,7 +2167,7 @@
         <v>136552369</v>
       </c>
       <c r="B16" t="n">
-        <v>108139</v>
+        <v>108152</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 50389-2025 artfynd.xlsx
+++ b/artfynd/A 50389-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136531087</v>
       </c>
       <c r="B2" t="n">
-        <v>99306</v>
+        <v>99308</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136533516</v>
       </c>
       <c r="B3" t="n">
-        <v>99306</v>
+        <v>99308</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>136533705</v>
       </c>
       <c r="B4" t="n">
-        <v>99306</v>
+        <v>99308</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>136536277</v>
       </c>
       <c r="B5" t="n">
-        <v>99306</v>
+        <v>99308</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1107,7 +1107,7 @@
         <v>136539184</v>
       </c>
       <c r="B6" t="n">
-        <v>99306</v>
+        <v>99308</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>136548232</v>
       </c>
       <c r="B7" t="n">
-        <v>99306</v>
+        <v>99308</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1319,7 +1319,7 @@
         <v>136548347</v>
       </c>
       <c r="B8" t="n">
-        <v>99306</v>
+        <v>99308</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1425,7 +1425,7 @@
         <v>136530741</v>
       </c>
       <c r="B9" t="n">
-        <v>108152</v>
+        <v>108154</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1531,7 +1531,7 @@
         <v>136531012</v>
       </c>
       <c r="B10" t="n">
-        <v>108152</v>
+        <v>108154</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1637,7 +1637,7 @@
         <v>136533686</v>
       </c>
       <c r="B11" t="n">
-        <v>108152</v>
+        <v>108154</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1743,7 +1743,7 @@
         <v>136534261</v>
       </c>
       <c r="B12" t="n">
-        <v>108152</v>
+        <v>108154</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1849,7 +1849,7 @@
         <v>136534775</v>
       </c>
       <c r="B13" t="n">
-        <v>108152</v>
+        <v>108154</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1955,7 +1955,7 @@
         <v>136538794</v>
       </c>
       <c r="B14" t="n">
-        <v>108152</v>
+        <v>108154</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2061,7 +2061,7 @@
         <v>136551802</v>
       </c>
       <c r="B15" t="n">
-        <v>108152</v>
+        <v>108154</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2167,7 +2167,7 @@
         <v>136552369</v>
       </c>
       <c r="B16" t="n">
-        <v>108152</v>
+        <v>108154</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
